--- a/dataset/mock_lease_data_completed.xlsx
+++ b/dataset/mock_lease_data_completed.xlsx
@@ -2,24 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lease Dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dataset Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PDF_Audit" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lease Dataset'!$A$1:$K$8</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,8 +31,14 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +47,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,18 +65,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -424,526 +479,1006 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Lease ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lease Start Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Lease End Date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Rent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Property Type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lease Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tenant Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Tenant Email</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PDF_File</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Extracted_Tenant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Extracted_Date</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Extracted_Address</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence_Score</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Match_Status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Match_Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Emily Carter</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>05/14/1992</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>125 Oak Street, Dallas, TX 75201</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ML-2025-1001</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>45658</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>46022</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>555-200-4100</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>emily.carter@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Michael Brown</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>11/23/1988</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>742 Pine Avenue, Austin, TX 78701</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>ML-2025-1002</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>45671</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>555-201-4101</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>michael.brown@example.com</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>ML-2025-1002_Michael_Brown.pdf</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>Michael Brown</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>1988-11-23</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>742 Pine Avenue, Austin, TX 78701</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>ADDRESS_FOUND</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>score: name_exact+40 lease_id+20 date+15 address_label+20 zip+10 street_number+5; address source: label (property address)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Wilson</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>07/09/1995</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>318 Cedar Lane, Houston, TX 77002</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ML-2025-1003</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>45684</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>46048</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1725</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Condominium</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>555-202-4102</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>sarah.wilson@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Daniel Martinez</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>02/18/1990</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>904 Maple Drive, Phoenix, AZ 85004</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>ML-2025-1004</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>45697</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>46061</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Single-Family Home</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>555-203-4103</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>daniel.martinez@example.com</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>ML-2025-1004_Daniel_Martinez.pdf</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>Daniel Martinez</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>1990-02-18</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>904 Maple Drive, Phoenix, AZ 85004</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>ADDRESS_FOUND</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>score: name_exact+40 lease_id+20 date+15 address_label+20 zip+10 street_number+5; address source: label (property address)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Olivia Thompson</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>09/27/1993</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>156 Willow Road, Denver, CO 80202</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>ML-2025-1005</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>45710</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>46074</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>555-204-4104</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>olivia.thompson@example.com</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>ML-2025-1005_Olivia_Thompson.pdf</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>Olivia Thompson</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>1993-09-27</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>156 Willow Road, Denver, CO 80202</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>ADDRESS_FOUND</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>score: name_exact+40 lease_id+20 date+15 address_label+20 zip+10 street_number+5; address source: label (property address)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>James Anderson</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>12/05/1986</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>481 Birch Court, Seattle, WA 98101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ML-2025-1006</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>45723</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>46087</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Condominium</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>555-205-4105</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>james.anderson@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sophia Lewis</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>03/21/1997</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>229 Aspen Way, Portland, OR 97205</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ML-2025-1007</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>45736</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>555-206-4106</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>sophia.lewis@example.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic dataset for AI document extraction, entity matching, and address reconciliation testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Address blanks</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>6 of 25 Excel records intentionally have blank Address values. Their complete addresses appear in the matching PDF lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Identity matching</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Name and DOB are identical between Excel and the corresponding PDF lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>All names, addresses, contact details, and lease identifiers are fictional test data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>PDF_File</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DOB</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Extracted_Tenant</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Lease ID</t>
+          <t>Extracted_Date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Lease Start Date</t>
+          <t>Extracted_Address</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Lease End Date</t>
+          <t>Matched_Excel_Row</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Monthly Rent</t>
+          <t>Matched_Name</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Property Type</t>
+          <t>Confidence_Score</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Lease Status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Tenant Phone</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tenant Email</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Extracted_Address</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Confidence_Score</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ML-2025-1001_Emily_Carter.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SKIPPED_ADDRESS_EXISTS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Emily Carter</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>05/14/1992</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1992-05-14</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>125 Oak Street, Dallas, TX 75201</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1001</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>45658</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>46022</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>555-200-4100</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>emily.carter@example.com</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>125 Oak Street, Dallas, TX 75201</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Emily Carter</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Matched record already has an address</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ML-2025-1002_Michael_Brown.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADDRESS_FOUND</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Michael Brown</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>11/23/1988</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1988-11-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>742 Pine Avenue, Austin, TX 78701</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1002</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>45671</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46035</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>555-201-4101</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>michael.brown@example.com</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>742 Pine Avenue, Austin, TX 78701</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Michael Brown</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>score: name_exact+40 lease_id+20 date+15 address_label+20 zip+10 street_number+5; address source: label (property address)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ML-2025-1003_Sarah_Wilson.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SKIPPED_ADDRESS_EXISTS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Sarah Wilson</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>07/09/1995</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1995-07-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>318 Cedar Lane, Houston, TX 77002</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1003</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>45684</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46048</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1725</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Condominium</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>555-202-4102</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>sarah.wilson@example.com</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>318 Cedar Lane, Houston, TX 77002</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarah Wilson</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Matched record already has an address</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ML-2025-1004_Daniel_Martinez.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADDRESS_FOUND</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Daniel Martinez</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>02/18/1990</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1990-02-18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>904 Maple Drive, Phoenix, AZ 85004</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1004</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>45697</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46061</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Single-Family Home</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>555-203-4103</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>daniel.martinez@example.com</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>904 Maple Drive, Phoenix, AZ 85004</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daniel Martinez</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>score: name_exact+40 lease_id+20 date+15 address_label+20 zip+10 street_number+5; address source: label (property address)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ML-2025-1005_Olivia_Thompson.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ADDRESS_FOUND</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Olivia Thompson</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>09/27/1993</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1993-09-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>156 Willow Road, Denver, CO 80202</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1005</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>45710</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46074</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>555-204-4104</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>olivia.thompson@example.com</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>156 Willow Road, Denver, CO 80202</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Olivia Thompson</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>score: name_exact+40 lease_id+20 date+15 address_label+20 zip+10 street_number+5; address source: label (property address)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ML-2025-1006_James_Anderson.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SKIPPED_ADDRESS_EXISTS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>James Anderson</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>12/05/1986</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1986-12-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>481 Birch Court, Seattle, WA 98101</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1006</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>45723</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46087</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2250</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Condominium</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>555-205-4105</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>james.anderson@example.com</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>481 Birch Court, Seattle, WA 98101</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>James Anderson</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Matched record already has an address</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ML-2025-1007_Sophia_Lewis.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SKIPPED_ADDRESS_EXISTS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Sophia Lewis</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>03/21/1997</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1997-03-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>229 Aspen Way, Portland, OR 97205</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ML-2025-1007</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>45736</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46100</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>555-206-4106</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>sophia.lewis@example.com</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>229 Aspen Way, Portland, OR 97205</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - Address found (1.00 &gt;= 0.80)</t>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sophia Lewis</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Matched record already has an address</t>
         </is>
       </c>
     </row>
